--- a/outputs/results/collocations_v2/marker_presence_check_clean_lexical_v2.xlsx
+++ b/outputs/results/collocations_v2/marker_presence_check_clean_lexical_v2.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,98 +542,98 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kein</t>
+          <t>kein_aktives_Todo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rückmeldung</t>
+          <t>kein</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>243</v>
+        <v>159</v>
       </c>
       <c r="C11" t="n">
-        <v>244</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gruppe</t>
+          <t>Rückmeldung</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>355</v>
+        <v>243</v>
       </c>
       <c r="C12" t="n">
-        <v>498</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>Gruppe</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>91</v>
+        <v>355</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>498</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="C14" t="n">
-        <v>136</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MT_Gruppe</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GT_Gruppe</t>
+          <t>MT_Gruppe</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -646,7 +646,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KT_Gruppe</t>
+          <t>GT_Gruppe</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -659,26 +659,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Raum</t>
+          <t>KT_Gruppe</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Raum</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>86</v>
+      </c>
+      <c r="C20" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>ÖGD</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" t="n">
         <v>76</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>80</v>
       </c>
     </row>
@@ -693,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,10 +811,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -811,152 +824,165 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="C9" t="n">
-        <v>662</v>
+        <v>712</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kein</t>
+          <t>kein_aktives_Todo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rückmeldung</t>
+          <t>kein</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>243</v>
+        <v>141</v>
       </c>
       <c r="C11" t="n">
-        <v>244</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gruppe</t>
+          <t>Rückmeldung</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="C12" t="n">
-        <v>376</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>Gruppe</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>268</v>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>133</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MT_Gruppe</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="C16" t="n">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GT_Gruppe</t>
+          <t>MT_Gruppe</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KT_Gruppe</t>
+          <t>GT_Gruppe</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Raum</t>
+          <t>KT_Gruppe</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="C19" t="n">
-        <v>118</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Raum</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>86</v>
+      </c>
+      <c r="C20" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>ÖGD</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" t="n">
         <v>76</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>80</v>
       </c>
     </row>
@@ -971,7 +997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1076,10 +1102,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -1089,152 +1115,165 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="C9" t="n">
-        <v>662</v>
+        <v>712</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kein</t>
+          <t>kein_aktives_Todo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rückmeldung</t>
+          <t>kein</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>243</v>
+        <v>141</v>
       </c>
       <c r="C11" t="n">
-        <v>244</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gruppe</t>
+          <t>Rückmeldung</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="C12" t="n">
-        <v>376</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>Gruppe</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>268</v>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>133</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MT_Gruppe</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="C16" t="n">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GT_Gruppe</t>
+          <t>MT_Gruppe</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KT_Gruppe</t>
+          <t>GT_Gruppe</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Raum</t>
+          <t>KT_Gruppe</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="C19" t="n">
-        <v>118</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Raum</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>86</v>
+      </c>
+      <c r="C20" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>ÖGD</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" t="n">
         <v>76</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>80</v>
       </c>
     </row>
